--- a/outputs/analysis/Custom_Drug/extracted_trials/empa_vs_placebo_2doses__RCT4_structured_extracted.xlsx
+++ b/outputs/analysis/Custom_Drug/extracted_trials/empa_vs_placebo_2doses__RCT4_structured_extracted.xlsx
@@ -3542,7 +3542,7 @@
       </c>
       <c r="AS4" s="6" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>days</t>
         </is>
       </c>
       <c r="AT4" s="6" t="n"/>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AS5" s="8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>weeks</t>
         </is>
       </c>
       <c r="AT5" s="8" t="n"/>
@@ -6795,124 +6795,88 @@
       <c r="IS8" s="6" t="n"/>
       <c r="IT8" s="6" t="n"/>
       <c r="IU8" s="6" t="n"/>
-      <c r="IV8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="IW8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="IX8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="IV8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="IW8" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="IX8" s="6" t="n">
+        <v>9.5</v>
       </c>
       <c r="IY8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="IZ8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JA8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JB8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="IZ8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA8" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="JB8" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JC8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JD8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JE8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JF8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="JD8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JE8" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="JF8" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JG8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JH8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JI8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JJ8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="JH8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JI8" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="JJ8" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JK8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JL8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JM8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JN8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="JL8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JM8" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="JN8" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JO8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JP8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JQ8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JR8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="JP8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JQ8" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="JR8" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JS8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -7550,88 +7514,124 @@
           <t>%</t>
         </is>
       </c>
-      <c r="IV9" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="IW9" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="IX9" s="8" t="n">
-        <v>9.5</v>
+      <c r="IV9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IW9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IX9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="IY9" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="IZ9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA9" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JB9" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IZ9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JA9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JB9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JC9" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JD9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JE9" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JF9" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JD9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JE9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JF9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JG9" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JH9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JI9" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JJ9" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JH9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JI9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JJ9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JK9" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JL9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JM9" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JN9" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JL9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JM9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JN9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JO9" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JP9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JQ9" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="JR9" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JP9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JQ9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JR9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JS9" s="8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AS10" s="6" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>days</t>
         </is>
       </c>
       <c r="AT10" s="6" t="n"/>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="AS11" s="8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>weeks</t>
         </is>
       </c>
       <c r="AT11" s="8" t="n"/>
@@ -11073,124 +11073,88 @@
       <c r="IS14" s="6" t="n"/>
       <c r="IT14" s="6" t="n"/>
       <c r="IU14" s="6" t="n"/>
-      <c r="IV14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="IW14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="IX14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="IV14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="IW14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="IX14" s="6" t="n">
+        <v>15</v>
       </c>
       <c r="IY14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="IZ14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JA14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JB14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="IZ14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="JB14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JC14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JD14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JE14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JF14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="JD14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JE14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="JF14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JG14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JH14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JI14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JJ14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="JH14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JI14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="JJ14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JK14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JL14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JM14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JN14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="JL14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JM14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="JN14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JO14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JP14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JQ14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JR14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="JP14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JQ14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="JR14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JS14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -11828,88 +11792,124 @@
           <t>%</t>
         </is>
       </c>
-      <c r="IV15" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="IW15" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="IX15" s="8" t="n">
-        <v>15</v>
+      <c r="IV15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IW15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IX15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="IY15" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="IZ15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA15" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JB15" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IZ15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JA15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JB15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JC15" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JD15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JE15" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JF15" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JD15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JE15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JF15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JG15" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JH15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JI15" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JJ15" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JH15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JI15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JJ15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JK15" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JL15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JM15" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JN15" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JL15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JM15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JN15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JO15" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JP15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JQ15" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="JR15" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JP15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JQ15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JR15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JS15" s="8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="AS16" s="6" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>days</t>
         </is>
       </c>
       <c r="AT16" s="6" t="n"/>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="AS17" s="8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>weeks</t>
         </is>
       </c>
       <c r="AT17" s="8" t="n"/>
@@ -15351,124 +15351,88 @@
       <c r="IS20" s="6" t="n"/>
       <c r="IT20" s="6" t="n"/>
       <c r="IU20" s="6" t="n"/>
-      <c r="IV20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="IW20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="IX20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="IV20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="IW20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="IX20" s="6" t="n">
+        <v>15.8</v>
       </c>
       <c r="IY20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="IZ20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JA20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JB20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="IZ20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="JB20" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JC20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JD20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JE20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JF20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="JD20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JE20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="JF20" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JG20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JH20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JI20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JJ20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="JH20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JI20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="JJ20" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JK20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JL20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JM20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JN20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="JL20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="JM20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="JN20" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="JO20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JP20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JQ20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="JR20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="JP20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="JQ20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="JR20" s="6" t="n">
+        <v>5.3</v>
       </c>
       <c r="JS20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -16106,88 +16070,124 @@
           <t>%</t>
         </is>
       </c>
-      <c r="IV21" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="IW21" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="IX21" s="8" t="n">
-        <v>15.8</v>
+      <c r="IV21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IW21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IX21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="IY21" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="IZ21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA21" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JB21" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="IZ21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JA21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JB21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JC21" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JD21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JE21" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JF21" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JD21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JE21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JF21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JG21" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JH21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JI21" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JJ21" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JH21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JI21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JJ21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JK21" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JL21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="JM21" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JN21" s="8" t="n">
-        <v>0</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JL21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JM21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JN21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JO21" s="8" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="JP21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="JQ21" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="JR21" s="8" t="n">
-        <v>5.3</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JP21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JQ21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="JR21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="JS21" s="8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
